--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1203,62 +1203,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1287,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,12 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,6 +1303,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2008,47 +2008,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2057,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R12" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,38 +2150,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,13 +2199,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R13" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,26 +2264,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129130011</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>129129938</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>129125217</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,48 +1076,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129125416</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520071</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001386</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,22 +1189,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129131247</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,17 +1238,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520503</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001232</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1287,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1315,14 +1314,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,62 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1434,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
         <v>129125920</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>129130596</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>129126187</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>129129973</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>129130055</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129130167</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3768,6 +3768,1526 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129193588</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>520524</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7001188</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129193525</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>520515</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7001222</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129193530</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>520173</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7001170</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129193531</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>520175</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7001165</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129193541</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>520428</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7001209</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129193532</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>520178</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7001163</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129193589</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>520455</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7001142</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129193528</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>520167</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7001172</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129193536</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>520274</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7001141</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129193529</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>520173</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7001174</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129193534</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>520235</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7001152</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129193535</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>520246</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7001145</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129193527</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>520572</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7001134</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129193537</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>520265</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7001135</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129193526</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>520534</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7001193</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,62 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1170,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
         <v>79035</v>
@@ -1238,17 +1234,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,9 +1315,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129126187</v>
+        <v>129130155</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,37 +2857,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520022</v>
+        <v>520230</v>
       </c>
       <c r="R18" t="n">
-        <v>7001485</v>
+        <v>7001153</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2916,7 +2926,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2926,7 +2936,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2955,12 +2970,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2978,7 +2993,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129129973</v>
+        <v>129126187</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -3009,17 +3024,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520374</v>
+        <v>520022</v>
       </c>
       <c r="R19" t="n">
-        <v>7001163</v>
+        <v>7001485</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3048,7 +3063,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3058,7 +3073,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3072,7 +3087,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3085,9 +3100,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3105,10 +3125,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129130155</v>
+        <v>129129973</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3116,47 +3136,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520230</v>
+        <v>520374</v>
       </c>
       <c r="R20" t="n">
-        <v>7001153</v>
+        <v>7001163</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3185,7 +3195,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3195,12 +3205,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3214,7 +3219,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3227,14 +3232,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -2008,38 +2008,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2048,13 +2057,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R12" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2083,7 +2092,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2102,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,26 +2122,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,47 +2139,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2199,13 +2179,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R13" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2224,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,6 +2244,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2578,48 +2578,67 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R16" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2648,7 +2667,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2658,7 +2677,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2673,26 +2697,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2710,67 +2714,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2799,7 +2784,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2809,12 +2794,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2829,6 +2809,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,48 +1076,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129125416</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520071</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001386</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,22 +1189,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129131247</v>
       </c>
       <c r="B6" t="n">
         <v>79035</v>
@@ -1234,17 +1238,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520503</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001232</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1287,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1315,14 +1314,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,62 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1434,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2578,67 +2578,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2667,7 +2648,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2677,12 +2658,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2697,6 +2673,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2714,48 +2710,67 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R17" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2784,7 +2799,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2794,7 +2809,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,26 +2829,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129130155</v>
+        <v>129126187</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,47 +2857,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520230</v>
+        <v>520022</v>
       </c>
       <c r="R18" t="n">
-        <v>7001153</v>
+        <v>7001485</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2926,7 +2916,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2936,12 +2926,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2970,12 +2955,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2993,7 +2978,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129126187</v>
+        <v>129129973</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -3024,17 +3009,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520022</v>
+        <v>520374</v>
       </c>
       <c r="R19" t="n">
-        <v>7001485</v>
+        <v>7001163</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3063,7 +3048,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,7 +3058,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3087,7 +3072,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3100,14 +3085,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3125,10 +3105,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129129973</v>
+        <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,37 +3116,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520374</v>
+        <v>520230</v>
       </c>
       <c r="R20" t="n">
-        <v>7001163</v>
+        <v>7001153</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3205,7 +3195,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3219,7 +3214,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3232,9 +3227,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125676</v>
+        <v>129130055</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,39 +3263,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520070</v>
+        <v>520308</v>
       </c>
       <c r="R21" t="n">
-        <v>7001411</v>
+        <v>7001138</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3327,7 +3322,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3337,7 +3332,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3348,31 +3343,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3389,7 +3359,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130055</v>
+        <v>129130167</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -3424,13 +3394,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520308</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001138</v>
+        <v>7001166</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3459,7 +3429,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3469,7 +3439,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3480,6 +3450,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3496,10 +3491,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130167</v>
+        <v>129125676</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,37 +3502,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520226</v>
+        <v>520070</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001411</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193536</v>
+        <v>129193529</v>
       </c>
       <c r="B33" t="n">
         <v>57723</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520274</v>
+        <v>520173</v>
       </c>
       <c r="R33" t="n">
-        <v>7001141</v>
+        <v>7001174</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4678,7 +4678,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193529</v>
+        <v>129193536</v>
       </c>
       <c r="B34" t="n">
         <v>57723</v>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520173</v>
+        <v>520274</v>
       </c>
       <c r="R34" t="n">
-        <v>7001174</v>
+        <v>7001141</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130011</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>129129938</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>129125217</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,62 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1170,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,17 +1234,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,9 +1315,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>129130136</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129125920</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>129131114</v>
       </c>
       <c r="B10" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>129130596</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>129125910</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>129125353</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>129126187</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>129129973</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,34 +3263,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R21" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3322,7 +3327,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3332,7 +3337,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3343,6 +3348,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3362,7 +3392,7 @@
         <v>129130167</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3491,10 +3521,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129125676</v>
+        <v>129130055</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3502,39 +3532,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520070</v>
+        <v>520308</v>
       </c>
       <c r="R23" t="n">
-        <v>7001411</v>
+        <v>7001138</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3566,7 +3591,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3601,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3587,31 +3612,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3631,7 +3631,7 @@
         <v>129130214</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>129193588</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>129193530</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>129193531</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129193541</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129193532</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193589</v>
+        <v>129193528</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4388,21 +4388,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520455</v>
+        <v>520167</v>
       </c>
       <c r="R31" t="n">
-        <v>7001142</v>
+        <v>7001172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4448,6 +4448,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4474,10 +4479,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193528</v>
+        <v>129193536</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4509,10 +4514,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520167</v>
+        <v>520274</v>
       </c>
       <c r="R32" t="n">
-        <v>7001172</v>
+        <v>7001141</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4549,7 +4554,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4579,7 +4584,7 @@
         <v>129193529</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4678,10 +4683,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193536</v>
+        <v>129193589</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4689,21 +4694,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4713,10 +4718,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520274</v>
+        <v>520455</v>
       </c>
       <c r="R34" t="n">
-        <v>7001141</v>
+        <v>7001142</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4749,11 +4754,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4783,7 +4783,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129193527</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129193526</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,48 +1076,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129125416</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520071</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001386</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,22 +1189,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129131247</v>
       </c>
       <c r="B6" t="n">
         <v>79039</v>
@@ -1234,17 +1238,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520503</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001232</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1287,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1315,14 +1314,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,62 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1434,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2008,47 +2008,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2057,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R12" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,38 +2150,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,13 +2199,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R13" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,26 +2264,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2578,48 +2578,67 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R16" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2648,7 +2667,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2658,7 +2677,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2673,26 +2697,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2710,67 +2714,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2799,7 +2784,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2809,12 +2794,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2829,6 +2809,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125676</v>
+        <v>129130055</v>
       </c>
       <c r="B21" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,39 +3263,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520070</v>
+        <v>520308</v>
       </c>
       <c r="R21" t="n">
-        <v>7001411</v>
+        <v>7001138</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3327,7 +3322,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3337,7 +3332,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3348,31 +3343,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3521,10 +3491,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3532,34 +3502,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R23" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3591,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3601,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3612,6 +3587,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -4377,10 +4377,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193528</v>
+        <v>129193589</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4388,21 +4388,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520167</v>
+        <v>520455</v>
       </c>
       <c r="R31" t="n">
-        <v>7001172</v>
+        <v>7001142</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4448,11 +4448,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4479,7 +4474,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193536</v>
+        <v>129193529</v>
       </c>
       <c r="B32" t="n">
         <v>57725</v>
@@ -4514,10 +4509,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520274</v>
+        <v>520173</v>
       </c>
       <c r="R32" t="n">
-        <v>7001141</v>
+        <v>7001174</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4554,7 +4549,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4581,7 +4576,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193529</v>
+        <v>129193528</v>
       </c>
       <c r="B33" t="n">
         <v>57725</v>
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520173</v>
+        <v>520167</v>
       </c>
       <c r="R33" t="n">
-        <v>7001174</v>
+        <v>7001172</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4683,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193589</v>
+        <v>129193536</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4694,21 +4689,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4718,10 +4713,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520455</v>
+        <v>520274</v>
       </c>
       <c r="R34" t="n">
-        <v>7001142</v>
+        <v>7001141</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4754,6 +4749,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130011</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>129129938</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>129125217</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,62 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1170,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,17 +1234,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,9 +1315,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>129130136</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129125920</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>129131114</v>
       </c>
       <c r="B10" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>129130596</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>129126104</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>129125940</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129126187</v>
+        <v>129130155</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,37 +2857,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520022</v>
+        <v>520230</v>
       </c>
       <c r="R18" t="n">
-        <v>7001485</v>
+        <v>7001153</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2916,7 +2926,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2926,7 +2936,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2955,12 +2970,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2978,10 +2993,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129129973</v>
+        <v>129126187</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3009,17 +3024,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520374</v>
+        <v>520022</v>
       </c>
       <c r="R19" t="n">
-        <v>7001163</v>
+        <v>7001485</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3048,7 +3063,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3058,7 +3073,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3072,7 +3087,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3085,9 +3100,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3105,10 +3125,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129130155</v>
+        <v>129129973</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3116,47 +3136,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520230</v>
+        <v>520374</v>
       </c>
       <c r="R20" t="n">
-        <v>7001153</v>
+        <v>7001163</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3185,7 +3195,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3195,12 +3205,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3214,7 +3219,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3227,14 +3232,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3255,7 +3255,7 @@
         <v>129130055</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>129130167</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>129125676</v>
       </c>
       <c r="B23" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129130214</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>129193588</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>129193530</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>129193531</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129193541</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129193532</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>129193589</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193529</v>
+        <v>129193528</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520173</v>
+        <v>520167</v>
       </c>
       <c r="R32" t="n">
-        <v>7001174</v>
+        <v>7001172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193528</v>
+        <v>129193536</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520167</v>
+        <v>520274</v>
       </c>
       <c r="R33" t="n">
-        <v>7001172</v>
+        <v>7001141</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193536</v>
+        <v>129193529</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520274</v>
+        <v>520173</v>
       </c>
       <c r="R34" t="n">
-        <v>7001141</v>
+        <v>7001174</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4783,7 +4783,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129193527</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129193526</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -2578,67 +2578,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2667,7 +2648,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2677,12 +2658,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2697,6 +2673,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2714,48 +2710,67 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R17" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2784,7 +2799,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2794,7 +2809,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,26 +2829,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129130155</v>
+        <v>129126187</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,47 +2857,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520230</v>
+        <v>520022</v>
       </c>
       <c r="R18" t="n">
-        <v>7001153</v>
+        <v>7001485</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2926,7 +2916,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2936,12 +2926,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2970,12 +2955,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2993,7 +2978,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129126187</v>
+        <v>129129973</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -3024,17 +3009,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520022</v>
+        <v>520374</v>
       </c>
       <c r="R19" t="n">
-        <v>7001485</v>
+        <v>7001163</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3063,7 +3048,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,7 +3058,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3087,7 +3072,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3100,14 +3085,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3125,10 +3105,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129129973</v>
+        <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,37 +3116,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520374</v>
+        <v>520230</v>
       </c>
       <c r="R20" t="n">
-        <v>7001163</v>
+        <v>7001153</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3205,7 +3195,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3219,7 +3214,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3232,9 +3227,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129130055</v>
+        <v>129130167</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520308</v>
+        <v>520226</v>
       </c>
       <c r="R21" t="n">
-        <v>7001138</v>
+        <v>7001166</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3343,6 +3343,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3359,7 +3384,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -3394,13 +3419,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R22" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3429,7 +3454,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,7 +3464,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3450,31 +3475,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -3252,7 +3252,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R21" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3343,31 +3343,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3384,10 +3359,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3395,34 +3370,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R22" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3454,7 +3434,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3464,7 +3444,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3475,6 +3455,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3491,10 +3496,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129125676</v>
+        <v>129130167</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3502,42 +3507,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520070</v>
+        <v>520226</v>
       </c>
       <c r="R23" t="n">
-        <v>7001411</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1343,7 +1343,7 @@
         <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129126187</v>
+        <v>129130155</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,37 +2857,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520022</v>
+        <v>520230</v>
       </c>
       <c r="R18" t="n">
-        <v>7001485</v>
+        <v>7001153</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2916,7 +2926,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2926,7 +2936,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2955,12 +2970,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2978,7 +2993,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129129973</v>
+        <v>129126187</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -3009,17 +3024,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520374</v>
+        <v>520022</v>
       </c>
       <c r="R19" t="n">
-        <v>7001163</v>
+        <v>7001485</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3048,7 +3063,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3058,7 +3073,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3072,7 +3087,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3085,9 +3100,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3105,10 +3125,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129130155</v>
+        <v>129129973</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3116,47 +3136,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520230</v>
+        <v>520374</v>
       </c>
       <c r="R20" t="n">
-        <v>7001153</v>
+        <v>7001163</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3185,7 +3195,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3195,12 +3205,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3214,7 +3219,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3227,14 +3232,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129125676</v>
+        <v>129130167</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3370,42 +3370,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520070</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001411</v>
+        <v>7001166</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3434,7 +3429,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3444,7 +3439,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3463,22 +3458,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3496,10 +3491,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130167</v>
+        <v>129125676</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,37 +3502,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520226</v>
+        <v>520070</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001411</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1343,7 +1343,7 @@
         <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2008,38 +2008,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2048,13 +2057,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R12" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2083,7 +2092,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2102,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,26 +2122,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,47 +2139,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2199,13 +2179,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R13" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2224,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,6 +2244,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,34 +3263,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R21" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3322,7 +3327,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3332,7 +3337,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3343,6 +3348,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3359,7 +3389,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -3394,13 +3424,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R22" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3429,7 +3459,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,7 +3469,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3450,31 +3480,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3491,10 +3496,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129125676</v>
+        <v>129130167</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3502,42 +3507,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520070</v>
+        <v>520226</v>
       </c>
       <c r="R23" t="n">
-        <v>7001411</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1343,7 +1343,7 @@
         <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2008,47 +2008,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2057,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R12" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,38 +2150,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,13 +2199,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R13" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,26 +2264,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2578,48 +2578,67 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R16" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2648,7 +2667,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2658,7 +2677,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2673,26 +2697,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2710,67 +2714,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2799,7 +2784,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2809,12 +2794,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2829,6 +2809,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125676</v>
+        <v>129130055</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,39 +3263,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520070</v>
+        <v>520308</v>
       </c>
       <c r="R21" t="n">
-        <v>7001411</v>
+        <v>7001138</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3327,7 +3322,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3337,7 +3332,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3348,31 +3343,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3389,7 +3359,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130055</v>
+        <v>129130167</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -3424,13 +3394,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520308</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001138</v>
+        <v>7001166</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3459,7 +3429,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3469,7 +3439,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3480,6 +3450,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3496,10 +3491,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130167</v>
+        <v>129125676</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,37 +3502,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520226</v>
+        <v>520070</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001411</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130011</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>129129938</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>129125217</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,17 +1107,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1175,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1183,9 +1188,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,48 +1213,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1297,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1307,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,26 +1327,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,62 +1344,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,7 +1438,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
         <v>129125920</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>129130596</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2008,38 +2008,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2048,13 +2057,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R12" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2083,7 +2092,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2102,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,26 +2122,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,47 +2139,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2199,13 +2179,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R13" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2224,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,6 +2244,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129125301</v>
+        <v>129125628</v>
       </c>
       <c r="B14" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520055</v>
+        <v>520073</v>
       </c>
       <c r="R14" t="n">
-        <v>7001387</v>
+        <v>7001402</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2375,12 +2375,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer i en gammal sälg med lunglav.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2432,10 +2427,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129125628</v>
+        <v>129125301</v>
       </c>
       <c r="B15" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2481,13 +2476,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520073</v>
+        <v>520055</v>
       </c>
       <c r="R15" t="n">
-        <v>7001402</v>
+        <v>7001387</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2516,7 +2511,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2526,7 +2521,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer i en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2578,67 +2578,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2667,7 +2648,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2677,12 +2658,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2697,6 +2673,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2714,48 +2710,67 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R17" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2784,7 +2799,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2794,7 +2809,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,26 +2829,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
         <v>129126187</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>129129973</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,34 +3263,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R21" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3322,7 +3327,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3332,7 +3337,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3343,6 +3348,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3359,10 +3389,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3394,13 +3424,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R22" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3429,7 +3459,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,7 +3469,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3450,31 +3480,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3491,10 +3496,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129125676</v>
+        <v>129130167</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3502,42 +3507,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520070</v>
+        <v>520226</v>
       </c>
       <c r="R23" t="n">
-        <v>7001411</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
         <v>129193588</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>129193589</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130011</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>129129938</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>129125217</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>129130544</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,62 +1213,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R6" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1297,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,12 +1293,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,7 +1307,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1344,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129131247</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520503</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001232</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1414,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,22 +1453,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
         <v>129125920</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>129130596</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2008,47 +2008,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2057,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R12" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,38 +2150,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,13 +2199,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R13" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,26 +2264,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129125628</v>
+        <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520073</v>
+        <v>520055</v>
       </c>
       <c r="R14" t="n">
-        <v>7001402</v>
+        <v>7001387</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2375,7 +2375,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer i en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2427,10 +2432,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129125301</v>
+        <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2457,7 +2462,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2476,13 +2481,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520055</v>
+        <v>520073</v>
       </c>
       <c r="R15" t="n">
-        <v>7001387</v>
+        <v>7001402</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2511,7 +2516,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2521,12 +2526,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer i en gammal sälg med lunglav.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2581,7 +2581,7 @@
         <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>129126187</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>129129973</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3389,10 +3389,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130055</v>
+        <v>129130167</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520308</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001138</v>
+        <v>7001166</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3480,6 +3480,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3496,10 +3521,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3531,13 +3556,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3591,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3601,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3587,31 +3612,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3773,7 +3773,7 @@
         <v>129193588</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>129193589</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,48 +1076,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R5" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,12 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,26 +1190,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1340,62 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1434,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
         <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125676</v>
+        <v>129130055</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,39 +3263,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520070</v>
+        <v>520308</v>
       </c>
       <c r="R21" t="n">
-        <v>7001411</v>
+        <v>7001138</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3327,7 +3322,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3337,7 +3332,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3348,31 +3343,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3521,10 +3491,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3532,34 +3502,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R23" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3591,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3601,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3612,6 +3587,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,62 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1170,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1238,17 +1234,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,9 +1315,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
         <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129130155</v>
+        <v>129126187</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,47 +2857,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520230</v>
+        <v>520022</v>
       </c>
       <c r="R18" t="n">
-        <v>7001153</v>
+        <v>7001485</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2926,7 +2916,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2936,12 +2926,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2970,12 +2955,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2993,7 +2978,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129126187</v>
+        <v>129129973</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -3024,17 +3009,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520022</v>
+        <v>520374</v>
       </c>
       <c r="R19" t="n">
-        <v>7001485</v>
+        <v>7001163</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3063,7 +3048,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,7 +3058,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3087,7 +3072,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3100,14 +3085,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3125,10 +3105,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129129973</v>
+        <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,37 +3116,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520374</v>
+        <v>520230</v>
       </c>
       <c r="R20" t="n">
-        <v>7001163</v>
+        <v>7001153</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3205,7 +3195,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3219,7 +3214,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3232,9 +3227,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,34 +3263,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R21" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3322,7 +3327,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3332,7 +3337,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3343,6 +3348,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3359,7 +3389,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -3394,13 +3424,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R22" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3429,7 +3459,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,7 +3469,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3450,31 +3480,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3491,10 +3496,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129125676</v>
+        <v>129130167</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3502,42 +3507,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520070</v>
+        <v>520226</v>
       </c>
       <c r="R23" t="n">
-        <v>7001411</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,48 +1076,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129125416</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520071</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001386</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,22 +1189,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129131247</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1234,17 +1238,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520503</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001232</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1287,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1315,14 +1314,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,62 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1434,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2008,38 +2008,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2048,13 +2057,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R12" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2083,7 +2092,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2102,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,26 +2122,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,47 +2139,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2199,13 +2179,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R13" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2224,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,6 +2244,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,62 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1170,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1238,17 +1234,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,9 +1315,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,7 +1076,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1107,17 +1107,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1175,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1183,9 +1188,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,7 +1213,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129131247</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1234,17 +1244,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520503</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001232</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1293,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1307,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1315,14 +1320,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
         <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2008,47 +2008,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2057,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R12" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,38 +2150,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,13 +2199,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R13" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,26 +2264,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2578,48 +2578,67 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R16" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2648,7 +2667,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2658,7 +2677,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2673,26 +2697,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2710,67 +2714,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2799,7 +2784,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2809,12 +2794,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2829,6 +2809,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130055</v>
+        <v>129130167</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520308</v>
+        <v>520226</v>
       </c>
       <c r="R22" t="n">
-        <v>7001138</v>
+        <v>7001166</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3480,6 +3480,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3496,7 +3521,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -3531,13 +3556,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3591,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3601,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3587,31 +3612,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,48 +1076,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R5" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,12 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,26 +1190,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1340,62 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1434,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2008,38 +2008,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2048,13 +2057,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R12" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2083,7 +2092,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2102,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,26 +2122,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,47 +2139,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2199,13 +2179,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R13" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2224,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,6 +2244,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2578,67 +2578,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2667,7 +2648,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2677,12 +2658,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2697,6 +2673,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2714,48 +2710,67 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R17" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2784,7 +2799,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2794,7 +2809,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,26 +2829,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125676</v>
+        <v>129130055</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,39 +3263,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520070</v>
+        <v>520308</v>
       </c>
       <c r="R21" t="n">
-        <v>7001411</v>
+        <v>7001138</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3327,7 +3322,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3337,7 +3332,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3348,31 +3343,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3521,10 +3491,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3532,34 +3502,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R23" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3591,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3601,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3612,6 +3587,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3969,7 +3969,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193530</v>
+        <v>129193541</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520173</v>
+        <v>520428</v>
       </c>
       <c r="R27" t="n">
-        <v>7001170</v>
+        <v>7001209</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193531</v>
+        <v>129193530</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520175</v>
+        <v>520173</v>
       </c>
       <c r="R28" t="n">
-        <v>7001165</v>
+        <v>7001170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193541</v>
+        <v>129193531</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520428</v>
+        <v>520175</v>
       </c>
       <c r="R29" t="n">
-        <v>7001209</v>
+        <v>7001165</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193528</v>
+        <v>129193536</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520167</v>
+        <v>520274</v>
       </c>
       <c r="R32" t="n">
-        <v>7001172</v>
+        <v>7001141</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4576,7 +4576,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193536</v>
+        <v>129193528</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520274</v>
+        <v>520167</v>
       </c>
       <c r="R33" t="n">
-        <v>7001141</v>
+        <v>7001172</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,62 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1170,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1238,17 +1234,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,9 +1315,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2008,47 +2008,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2057,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R12" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,38 +2150,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,13 +2199,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R13" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,26 +2264,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193541</v>
+        <v>129193530</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520428</v>
+        <v>520173</v>
       </c>
       <c r="R27" t="n">
-        <v>7001209</v>
+        <v>7001170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193530</v>
+        <v>129193531</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520173</v>
+        <v>520175</v>
       </c>
       <c r="R28" t="n">
-        <v>7001170</v>
+        <v>7001165</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193531</v>
+        <v>129193541</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520175</v>
+        <v>520428</v>
       </c>
       <c r="R29" t="n">
-        <v>7001165</v>
+        <v>7001209</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193536</v>
+        <v>129193528</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520274</v>
+        <v>520167</v>
       </c>
       <c r="R32" t="n">
-        <v>7001141</v>
+        <v>7001172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4576,7 +4576,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193528</v>
+        <v>129193536</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520167</v>
+        <v>520274</v>
       </c>
       <c r="R33" t="n">
-        <v>7001172</v>
+        <v>7001141</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -2008,38 +2008,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2048,13 +2057,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R12" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2083,7 +2092,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2102,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,26 +2122,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,47 +2139,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2199,13 +2179,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R13" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2224,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2264,6 +2244,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193534</v>
+        <v>129193535</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520235</v>
+        <v>520246</v>
       </c>
       <c r="R35" t="n">
-        <v>7001152</v>
+        <v>7001145</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193535</v>
+        <v>129193534</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520246</v>
+        <v>520235</v>
       </c>
       <c r="R36" t="n">
-        <v>7001145</v>
+        <v>7001152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,48 +1076,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129125416</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520071</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001386</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1160,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1170,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,22 +1189,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129131247</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1234,17 +1238,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520503</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001232</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1287,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1315,14 +1314,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,62 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129130544</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520471</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001136</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1434,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2008,47 +2008,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125910</v>
+        <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2057,13 +2048,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520074</v>
+        <v>520072</v>
       </c>
       <c r="R12" t="n">
-        <v>7001406</v>
+        <v>7001389</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,38 +2150,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125353</v>
+        <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2179,13 +2199,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520072</v>
+        <v>520074</v>
       </c>
       <c r="R13" t="n">
-        <v>7001389</v>
+        <v>7001406</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2244,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,26 +2264,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129126187</v>
+        <v>129130155</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,37 +2857,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520022</v>
+        <v>520230</v>
       </c>
       <c r="R18" t="n">
-        <v>7001485</v>
+        <v>7001153</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2916,7 +2926,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2926,7 +2936,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2955,12 +2970,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2978,7 +2993,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129129973</v>
+        <v>129126187</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -3009,17 +3024,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520374</v>
+        <v>520022</v>
       </c>
       <c r="R19" t="n">
-        <v>7001163</v>
+        <v>7001485</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3048,7 +3063,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3058,7 +3073,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3072,7 +3087,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3085,9 +3100,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3105,10 +3125,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129130155</v>
+        <v>129129973</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3116,47 +3136,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520230</v>
+        <v>520374</v>
       </c>
       <c r="R20" t="n">
-        <v>7001153</v>
+        <v>7001163</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3185,7 +3195,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3195,12 +3205,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3214,7 +3219,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3227,14 +3232,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193535</v>
+        <v>129193534</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520246</v>
+        <v>520235</v>
       </c>
       <c r="R35" t="n">
-        <v>7001145</v>
+        <v>7001152</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193534</v>
+        <v>129193535</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520235</v>
+        <v>520246</v>
       </c>
       <c r="R36" t="n">
-        <v>7001152</v>
+        <v>7001145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1076,62 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129125416</v>
+        <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520071</v>
+        <v>520503</v>
       </c>
       <c r="R5" t="n">
-        <v>7001386</v>
+        <v>7001232</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1170,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1170,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129131247</v>
+        <v>129130544</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1238,17 +1234,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520503</v>
+        <v>520471</v>
       </c>
       <c r="R6" t="n">
-        <v>7001232</v>
+        <v>7001136</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1314,9 +1315,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,48 +1340,62 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129130544</v>
+        <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520471</v>
+        <v>520071</v>
       </c>
       <c r="R7" t="n">
-        <v>7001136</v>
+        <v>7001386</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,12 +1434,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,26 +1454,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2578,48 +2578,67 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R16" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2648,7 +2667,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2658,7 +2677,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2673,26 +2697,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2710,67 +2714,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2799,7 +2784,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2809,12 +2794,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2829,6 +2809,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129130155</v>
+        <v>129126187</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2857,47 +2857,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520230</v>
+        <v>520022</v>
       </c>
       <c r="R18" t="n">
-        <v>7001153</v>
+        <v>7001485</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2926,7 +2916,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2936,12 +2926,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2970,12 +2955,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2993,7 +2978,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129126187</v>
+        <v>129129973</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -3024,17 +3009,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520022</v>
+        <v>520374</v>
       </c>
       <c r="R19" t="n">
-        <v>7001485</v>
+        <v>7001163</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3063,7 +3048,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3073,7 +3058,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3087,7 +3072,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3100,14 +3085,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3125,10 +3105,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129129973</v>
+        <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,37 +3116,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520374</v>
+        <v>520230</v>
       </c>
       <c r="R20" t="n">
-        <v>7001163</v>
+        <v>7001153</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3205,7 +3195,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3219,7 +3214,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3232,9 +3227,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129130055</v>
+        <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3263,34 +3263,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520308</v>
+        <v>520070</v>
       </c>
       <c r="R21" t="n">
-        <v>7001138</v>
+        <v>7001411</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3322,7 +3327,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3332,7 +3337,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3343,6 +3348,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3359,7 +3389,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130167</v>
+        <v>129130055</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -3394,13 +3424,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520226</v>
+        <v>520308</v>
       </c>
       <c r="R22" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3429,7 +3459,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3439,7 +3469,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3450,31 +3480,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3491,10 +3496,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129125676</v>
+        <v>129130167</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3502,42 +3507,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520070</v>
+        <v>520226</v>
       </c>
       <c r="R23" t="n">
-        <v>7001411</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193531</v>
+        <v>129193541</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520175</v>
+        <v>520428</v>
       </c>
       <c r="R28" t="n">
-        <v>7001165</v>
+        <v>7001209</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193541</v>
+        <v>129193531</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520428</v>
+        <v>520175</v>
       </c>
       <c r="R29" t="n">
-        <v>7001209</v>
+        <v>7001165</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193536</v>
+        <v>129193529</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520274</v>
+        <v>520173</v>
       </c>
       <c r="R33" t="n">
-        <v>7001141</v>
+        <v>7001174</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4678,7 +4678,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193529</v>
+        <v>129193536</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520173</v>
+        <v>520274</v>
       </c>
       <c r="R34" t="n">
-        <v>7001174</v>
+        <v>7001141</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130011</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>129129938</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>129125217</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>129131247</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>129130544</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129125416</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129130136</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129125920</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>129131114</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>129130596</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>129125353</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129125910</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129125301</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>129125628</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2578,67 +2578,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129126104</v>
+        <v>129125940</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520072</v>
+        <v>520054</v>
       </c>
       <c r="R16" t="n">
-        <v>7001412</v>
+        <v>7001432</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2667,7 +2648,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2677,12 +2658,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2697,6 +2673,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2714,48 +2710,67 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129125940</v>
+        <v>129126104</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520054</v>
+        <v>520072</v>
       </c>
       <c r="R17" t="n">
-        <v>7001432</v>
+        <v>7001412</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2784,7 +2799,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2794,7 +2809,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,26 +2829,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2849,7 +2849,7 @@
         <v>129126187</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>129129973</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>129125676</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>129130055</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129130167</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129130214</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>129193588</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>129193530</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193541</v>
+        <v>129193531</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520428</v>
+        <v>520175</v>
       </c>
       <c r="R28" t="n">
-        <v>7001209</v>
+        <v>7001165</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193531</v>
+        <v>129193541</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520175</v>
+        <v>520428</v>
       </c>
       <c r="R29" t="n">
-        <v>7001165</v>
+        <v>7001209</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4278,7 +4278,7 @@
         <v>129193532</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>129193589</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>129193528</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193529</v>
+        <v>129193536</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520173</v>
+        <v>520274</v>
       </c>
       <c r="R33" t="n">
-        <v>7001174</v>
+        <v>7001141</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4678,10 +4678,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193536</v>
+        <v>129193529</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520274</v>
+        <v>520173</v>
       </c>
       <c r="R34" t="n">
-        <v>7001141</v>
+        <v>7001174</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4783,7 +4783,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129193527</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129193526</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1474,7 +1474,7 @@
         <v>129130136</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129130214</v>
       </c>
       <c r="B24" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>129193530</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>129193531</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129193541</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129193532</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>129193528</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129193536</v>
       </c>
       <c r="B33" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>129193529</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129193527</v>
       </c>
       <c r="B37" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129193526</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1474,7 +1474,7 @@
         <v>129130136</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129130214</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>129193530</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>129193531</v>
       </c>
       <c r="B28" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129193541</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129193532</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>129193528</v>
       </c>
       <c r="B32" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129193536</v>
       </c>
       <c r="B33" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>129193529</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129193527</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129193526</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1474,7 +1474,7 @@
         <v>129130136</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129130214</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>129193530</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>129193531</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129193541</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129193532</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>129193528</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129193536</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>129193529</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129193527</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129193526</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -1474,7 +1474,7 @@
         <v>129130136</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>129130155</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129130214</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>129193530</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>129193531</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129193541</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129193532</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>129193528</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129193536</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>129193529</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129193527</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129193526</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129130011</v>
+        <v>129125301</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520368</v>
+        <v>520055</v>
       </c>
       <c r="R2" t="n">
-        <v>7001135</v>
+        <v>7001387</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer i en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +788,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,48 +826,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129129938</v>
+        <v>129125628</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520392</v>
+        <v>520073</v>
       </c>
       <c r="R3" t="n">
-        <v>7001169</v>
+        <v>7001402</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +920,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +934,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,11 +975,11 @@
         <v>129125217</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1076,14 +1109,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129131247</v>
+        <v>129125920</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1111,13 +1144,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520503</v>
+        <v>520096</v>
       </c>
       <c r="R5" t="n">
-        <v>7001232</v>
+        <v>7001421</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1179,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1189,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1203,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1183,9 +1216,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,14 +1241,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129130544</v>
+        <v>129125940</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1234,17 +1272,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520471</v>
+        <v>520054</v>
       </c>
       <c r="R6" t="n">
-        <v>7001136</v>
+        <v>7001432</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1311,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1283,12 +1321,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1340,10 +1373,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129125416</v>
+        <v>129126187</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,51 +1384,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520071</v>
+        <v>520022</v>
       </c>
       <c r="R7" t="n">
-        <v>7001386</v>
+        <v>7001485</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1424,7 +1443,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,12 +1453,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,6 +1468,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1471,58 +1505,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129130136</v>
+        <v>129129938</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520242</v>
+        <v>520392</v>
       </c>
       <c r="R8" t="n">
-        <v>7001142</v>
+        <v>7001169</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1551,7 +1575,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1561,12 +1585,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, högt upp på en tall vid vägen.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1580,27 +1599,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1618,14 +1632,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129125920</v>
+        <v>129129973</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1649,14 +1663,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520096</v>
+        <v>520374</v>
       </c>
       <c r="R9" t="n">
-        <v>7001421</v>
+        <v>7001163</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1688,7 +1702,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,7 +1712,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1712,7 +1726,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1725,14 +1739,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1750,57 +1759,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131114</v>
+        <v>129130011</v>
       </c>
       <c r="B10" t="n">
-        <v>57834</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520560</v>
+        <v>520368</v>
       </c>
       <c r="R10" t="n">
-        <v>7001130</v>
+        <v>7001135</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Synobservation av 1 eller möjligen 2 lavskrikor.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1858,7 +1858,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1876,14 +1896,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129130596</v>
+        <v>129130055</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1911,13 +1931,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520560</v>
+        <v>520308</v>
       </c>
       <c r="R11" t="n">
-        <v>7001166</v>
+        <v>7001138</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1946,7 +1966,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1956,7 +1976,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,31 +1987,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2008,53 +2003,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129125353</v>
+        <v>129130167</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520072</v>
+        <v>520226</v>
       </c>
       <c r="R12" t="n">
-        <v>7001389</v>
+        <v>7001166</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2083,7 +2073,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2083,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2117,22 +2102,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,10 +2135,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129125910</v>
+        <v>129130443</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,51 +2146,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520074</v>
+        <v>520479</v>
       </c>
       <c r="R13" t="n">
-        <v>7001406</v>
+        <v>7001058</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2234,7 +2205,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2244,12 +2215,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2260,11 +2226,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2281,10 +2242,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129125301</v>
+        <v>129130544</v>
       </c>
       <c r="B14" t="n">
-        <v>92176</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2292,51 +2253,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520055</v>
+        <v>520471</v>
       </c>
       <c r="R14" t="n">
-        <v>7001387</v>
+        <v>7001136</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2365,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2375,12 +2322,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer i en gammal sälg med lunglav.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2399,22 +2346,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2432,10 +2379,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129125628</v>
+        <v>129130596</v>
       </c>
       <c r="B15" t="n">
-        <v>92176</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2443,48 +2390,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520073</v>
+        <v>520560</v>
       </c>
       <c r="R15" t="n">
-        <v>7001402</v>
+        <v>7001166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2516,7 +2449,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2526,7 +2459,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2545,22 +2478,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2578,14 +2511,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129125940</v>
+        <v>129131247</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2613,13 +2546,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520054</v>
+        <v>520503</v>
       </c>
       <c r="R16" t="n">
-        <v>7001432</v>
+        <v>7001232</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2648,7 +2581,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2658,7 +2591,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2672,7 +2605,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2685,14 +2618,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2710,10 +2638,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129126104</v>
+        <v>129193588</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2721,53 +2649,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520072</v>
+        <v>520524</v>
       </c>
       <c r="R17" t="n">
-        <v>7001412</v>
+        <v>7001188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2797,26 +2706,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2825,35 +2719,30 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129126187</v>
+        <v>129193589</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2877,14 +2766,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kajsadalen, Kajsadalen, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520022</v>
+        <v>520455</v>
       </c>
       <c r="R18" t="n">
-        <v>7001485</v>
+        <v>7001142</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2914,21 +2803,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2937,51 +2816,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129129973</v>
+        <v>129125353</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2989,37 +2843,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520374</v>
+        <v>520072</v>
       </c>
       <c r="R19" t="n">
-        <v>7001163</v>
+        <v>7001389</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3048,7 +2907,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3058,7 +2917,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3072,22 +2936,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3105,10 +2974,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129130155</v>
+        <v>129125676</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3116,44 +2985,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520230</v>
+        <v>520070</v>
       </c>
       <c r="R20" t="n">
-        <v>7001153</v>
+        <v>7001411</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -3185,7 +3049,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3195,12 +3059,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3219,22 +3078,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3252,10 +3111,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129125676</v>
+        <v>129127211</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3292,13 +3151,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520070</v>
+        <v>520158</v>
       </c>
       <c r="R21" t="n">
-        <v>7001411</v>
+        <v>7001448</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3327,7 +3186,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3337,7 +3196,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3351,7 +3210,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3389,10 +3248,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129130055</v>
+        <v>129193565</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3400,37 +3259,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520308</v>
+        <v>520156</v>
       </c>
       <c r="R22" t="n">
-        <v>7001138</v>
+        <v>7001442</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3457,19 +3316,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3484,22 +3333,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129130167</v>
+        <v>129130136</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3507,37 +3356,47 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520226</v>
+        <v>520242</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001142</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,7 +3425,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3576,7 +3435,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, högt upp på en tall vid vägen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3595,22 +3459,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3628,10 +3492,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129130214</v>
+        <v>129130155</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,19 +3526,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520193</v>
+        <v>520230</v>
       </c>
       <c r="R24" t="n">
-        <v>7001160</v>
+        <v>7001153</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3703,7 +3572,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3713,12 +3582,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, färska.</t>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3770,10 +3639,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129193588</v>
+        <v>129130214</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3781,37 +3650,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520524</v>
+        <v>520193</v>
       </c>
       <c r="R25" t="n">
-        <v>7001188</v>
+        <v>7001160</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3838,11 +3712,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, färska.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3851,16 +3740,41 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3870,7 +3784,7 @@
         <v>129193525</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3969,10 +3883,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193530</v>
+        <v>129193526</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4004,10 +3918,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520173</v>
+        <v>520534</v>
       </c>
       <c r="R27" t="n">
-        <v>7001170</v>
+        <v>7001193</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4044,7 +3958,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4071,10 +3985,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193531</v>
+        <v>129193527</v>
       </c>
       <c r="B28" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4106,10 +4020,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520175</v>
+        <v>520572</v>
       </c>
       <c r="R28" t="n">
-        <v>7001165</v>
+        <v>7001134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4173,10 +4087,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193541</v>
+        <v>129193528</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4208,10 +4122,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520428</v>
+        <v>520167</v>
       </c>
       <c r="R29" t="n">
-        <v>7001209</v>
+        <v>7001172</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4275,10 +4189,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193532</v>
+        <v>129193529</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,10 +4224,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520178</v>
+        <v>520173</v>
       </c>
       <c r="R30" t="n">
-        <v>7001163</v>
+        <v>7001174</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4377,10 +4291,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193589</v>
+        <v>129193530</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4388,21 +4302,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4412,10 +4326,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520455</v>
+        <v>520173</v>
       </c>
       <c r="R31" t="n">
-        <v>7001142</v>
+        <v>7001170</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4448,6 +4362,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4474,10 +4393,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193528</v>
+        <v>129193531</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4509,10 +4428,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520167</v>
+        <v>520175</v>
       </c>
       <c r="R32" t="n">
-        <v>7001172</v>
+        <v>7001165</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4576,10 +4495,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193536</v>
+        <v>129193532</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4611,10 +4530,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520274</v>
+        <v>520178</v>
       </c>
       <c r="R33" t="n">
-        <v>7001141</v>
+        <v>7001163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4651,7 +4570,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4678,10 +4597,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193529</v>
+        <v>129193533</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4713,10 +4632,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520173</v>
+        <v>520181</v>
       </c>
       <c r="R34" t="n">
-        <v>7001174</v>
+        <v>7001159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4783,7 +4702,7 @@
         <v>129193534</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4885,7 +4804,7 @@
         <v>129193535</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4984,10 +4903,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193527</v>
+        <v>129193536</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5019,10 +4938,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520572</v>
+        <v>520274</v>
       </c>
       <c r="R37" t="n">
-        <v>7001134</v>
+        <v>7001141</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5059,7 +4978,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5089,7 +5008,7 @@
         <v>129193537</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5188,10 +5107,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129193526</v>
+        <v>129193539</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5223,10 +5142,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520534</v>
+        <v>520278</v>
       </c>
       <c r="R39" t="n">
-        <v>7001193</v>
+        <v>7001123</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5263,7 +5182,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5287,6 +5206,734 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129193540</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>520268</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7001125</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129193541</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>520428</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7001209</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129131114</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storflon, Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>520560</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7001130</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 eller möjligen 2 lavskrikor.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129125416</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>520071</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7001386</v>
+      </c>
+      <c r="S43" t="n">
+        <v>12</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129125910</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>520074</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7001406</v>
+      </c>
+      <c r="S44" t="n">
+        <v>11</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129126104</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kajsadalen, Kajsadalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>520072</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7001412</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 2 fröställningar inom ca 2 x 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47115-2025 artfynd.xlsx
+++ b/artfynd/A 47115-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -823,6 +828,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -969,6 +979,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1106,6 +1121,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125217</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1238,6 +1258,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1370,6 +1395,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125940</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1502,6 +1532,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126187</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1629,6 +1664,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129938</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1756,6 +1796,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129973</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1893,6 +1938,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130011</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2000,6 +2050,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130055</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2132,6 +2187,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130167</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2239,6 +2299,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130443</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2376,6 +2441,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130544</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2508,6 +2578,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130596</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2635,6 +2710,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131247</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2732,6 +2812,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193588</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2829,6 +2914,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193589</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2971,6 +3061,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125353</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3108,6 +3203,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125676</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3245,6 +3345,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129127211</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3342,6 +3447,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193565</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3489,6 +3599,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130136</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3636,6 +3751,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130155</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3778,6 +3898,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130214</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3880,6 +4005,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193525</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3982,6 +4112,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193526</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4084,6 +4219,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193527</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4186,6 +4326,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193528</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4288,6 +4433,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193529</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4390,6 +4540,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193530</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4492,6 +4647,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193531</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4594,6 +4754,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193532</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4696,6 +4861,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193533</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4798,6 +4968,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193534</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4900,6 +5075,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193535</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5002,6 +5182,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193536</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5104,6 +5289,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193537</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5206,6 +5396,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193539</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5308,6 +5503,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193540</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5410,6 +5610,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193541</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5536,6 +5741,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131114</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5667,6 +5877,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125416</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5798,6 +6013,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129125910</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5934,8 +6154,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129126104</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>